--- a/task5/task5-aditional-tasks.xlsx
+++ b/task5/task5-aditional-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husey\Desktop\pjatk 2. semester\rbd\task5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5624D32-1797-4FD3-8BFF-EBCA18640F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C05523-0C67-4B0D-98FD-64F6E5CD3EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{841F86B4-78D6-40BB-9234-0EB819B61383}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="40">
   <si>
     <t>BCNF</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>D,B,E</t>
+  </si>
+  <si>
+    <t>K4 = D,E,B</t>
+  </si>
+  <si>
+    <t>A,C</t>
   </si>
 </sst>
 </file>
@@ -228,7 +234,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -241,6 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{600B2DA3-1C5F-4C7E-BFB5-768C92FEED27}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -590,41 +598,40 @@
     <col min="13" max="13" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -634,10 +641,8 @@
       <c r="L9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>4</v>
       </c>
@@ -651,33 +656,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="H12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -686,24 +691,24 @@
       <c r="G13" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="H13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -712,23 +717,23 @@
       <c r="G14" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -751,7 +756,6 @@
       <c r="J22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H23" s="4"/>
@@ -794,19 +798,19 @@
       <c r="G26" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="9" t="s">
+      <c r="H26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -814,19 +818,19 @@
       <c r="G27" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" s="10" t="s">
+      <c r="H27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -834,19 +838,19 @@
       <c r="G28" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L28" s="10" t="s">
+      <c r="H28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -854,19 +858,19 @@
       <c r="G29" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" s="9" t="s">
+      <c r="H29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -885,7 +889,6 @@
       <c r="J35" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K35" s="5"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H36" s="4"/>
@@ -936,73 +939,79 @@
       <c r="G39" t="s">
         <v>26</v>
       </c>
-      <c r="H39" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="8" t="s">
+      <c r="H39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="G40" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="8" t="s">
+      <c r="H40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1</v>
-      </c>
       <c r="G41" t="s">
         <v>12</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K41" s="7" t="s">
+      <c r="H41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
       <c r="G42" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42" s="7" t="s">
+      <c r="H42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1010,17 +1019,17 @@
       <c r="G43" t="s">
         <v>29</v>
       </c>
-      <c r="H43" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>19</v>
+      <c r="H43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
